--- a/docbox/testdata/sample.xlsx
+++ b/docbox/testdata/sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="预算" sheetId="1" r:id="rId1"/>
+    <sheet name="清单" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -401,35 +401,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>姓名</v>
+        <v>名称</v>
       </c>
       <c r="B1" t="str">
-        <v>部门</v>
+        <v>数量</v>
       </c>
       <c r="C1" t="str">
-        <v>金额</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>张三</v>
-      </c>
-      <c r="B2" t="str">
-        <v>研发</v>
-      </c>
-      <c r="C2">
-        <v>1200</v>
+        <v>服务器</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="str">
+        <v>机房 A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>李四</v>
-      </c>
-      <c r="B3" t="str">
-        <v>设计</v>
-      </c>
-      <c r="C3">
-        <v>980</v>
+        <v>笔记本</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="str">
+        <v>库存</v>
       </c>
     </row>
   </sheetData>
